--- a/config/auto_configs/2021_Hyundai_Kia_Niro(DE EV)_100kW_150kW.xlsx
+++ b/config/auto_configs/2021_Hyundai_Kia_Niro(DE EV)_100kW_150kW.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="VIN_YMME" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="NWS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VIN_YMME" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NWS" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,17 +520,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>KMA_00255</t>
+          <t>KMA_002B8</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>C110913</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>C110913</t>
+          <t>C111401</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -574,7 +574,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>C111401</t>
+          <t>C126801</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>C126801</t>
+          <t>C128302</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>C128302</t>
+          <t>C128504</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>C128504</t>
+          <t>C135801</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>C135801</t>
+          <t>C150301</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>C150301</t>
+          <t>C16134A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>C16134A</t>
+          <t>C163808</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>C163808</t>
+          <t>C165008</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>C165008</t>
+          <t>C16B808</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>C16B808</t>
+          <t>C224406</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>C224406</t>
+          <t>C238001</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>C238001</t>
+          <t>C24024B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>C24024B</t>
+          <t>C240271</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>C240271</t>
+          <t>C240428</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>C240428</t>
+          <t>C240527</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>C240527</t>
+          <t>C241619</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>C241619</t>
+          <t>C241719</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>C241719</t>
+          <t>C243078</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -960,17 +960,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>SRS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>KMA_002B8</t>
+          <t>KMA_00254</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>C243078</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>KMA_00254</t>
+          <t>KMA_00255</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -996,6 +996,622 @@
         </is>
       </c>
       <c r="D23" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>IBU-TPMS</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>KMA_0025D</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A/C</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>KMA_0033C</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>AAF</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>KMA_0025B</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ADM</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>KMA_001CA</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>AMP</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>KMA_HK_00022</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>AVN</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>KMA_HK_00023</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>BCW-L</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>KMA_002BC</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BCW-R</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>KMA_002BD</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>BMS</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>KMA_0035A</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>CCM</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>KMA_002BA</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>CLU</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>KMA_00292</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>DDM</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>KMA_001C6</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>KMA_0028A</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>E-Shifter</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>KMA_002BE</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>FCA</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>KMA_002B7</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>IBU-BCM</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>KMA_0025C</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>IGPM</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>KMA_00283</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>MCU</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>KMA_002B4</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>MFC</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>KMA_002BB</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>MLM</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>KMA_002BF</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>OBC</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>KMA_002B9</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>OCS</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>KMA_00180</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>PSM</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>KMA_002AD</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>RVMS</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>KMA_00257</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>KMA_00213</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>VCS/LDC</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>KMA_002B6</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>VESS</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>KMA_0025E</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>WPC</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>KMA_001C2</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
         <is>
           <t>00</t>
         </is>
